--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4979-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4979-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58EC2FC-394A-4207-9268-49AD5A0EDBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87CFD6BA-4F0A-48BB-85BD-F25086CE2DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{7102B044-16C0-4E74-81AB-CA510AB64D87}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E4D9B3DF-272C-44E4-B758-67D004B00D09}"/>
   </bookViews>
   <sheets>
     <sheet name="4979-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,22 +1400,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2DD759-0BC2-4D00-8A0C-AD3893A81B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308964AC-A121-476F-B50F-544E8263A01B}">
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1473,7 +1473,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1569,7 +1569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
         <v>25</v>
       </c>
